--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:06</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:32</t>
+    <t xml:space="preserve">2026-10-02 14:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:06</t>
+    <t xml:space="preserve">2026-10-04 08:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:56</t>
+    <t xml:space="preserve">2026-10-05 10:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -609,7 +609,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1418587.62</v>
+        <v>1418587.63</v>
       </c>
     </row>
     <row r="4">
@@ -694,7 +694,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1279456.12</v>
+        <v>1279456.13</v>
       </c>
     </row>
     <row r="9">
@@ -779,7 +779,7 @@
         <v>2024</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1224728.12</v>
+        <v>1224728.13</v>
       </c>
     </row>
     <row r="14">
@@ -830,7 +830,7 @@
         <v>2024</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1148017.12</v>
+        <v>1148017.13</v>
       </c>
     </row>
     <row r="17">
@@ -949,7 +949,7 @@
         <v>2024</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1105685.12</v>
+        <v>1105685.13</v>
       </c>
     </row>
     <row r="24">
@@ -966,7 +966,7 @@
         <v>2024</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1100827.62</v>
+        <v>1100827.63</v>
       </c>
     </row>
     <row r="25">
@@ -1034,7 +1034,7 @@
         <v>2024</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1071413.12</v>
+        <v>1071413.13</v>
       </c>
     </row>
     <row r="29">
@@ -1153,7 +1153,7 @@
         <v>2024</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1025549.62</v>
+        <v>1025549.63</v>
       </c>
     </row>
     <row r="36">
@@ -1170,7 +1170,7 @@
         <v>2024</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1012295.62</v>
+        <v>1012295.63</v>
       </c>
     </row>
     <row r="37">
